--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G4">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G10">

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="G14">

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q16">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -644,55 +644,55 @@
         <v>3.46</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>3.22</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>3.9</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>3.49</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1133,55 +1133,55 @@
         <v>1.43</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>2.29</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>7.95</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>4.33</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>4.36</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>2.03</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA15">
         <v>1.85</v>
@@ -2799,19 +2799,19 @@
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>4.68</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>2.67</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17">
         <v>2.05</v>
@@ -3125,19 +3125,19 @@
         <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>3.46</v>
+        <v>2.73</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S2">
         <v>1.44</v>
@@ -656,7 +656,7 @@
         <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V2">
         <v>1.31</v>
@@ -665,31 +665,31 @@
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
         <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="AA2">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
         <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
         <v>1.8</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
         <v>1.5</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="O3">
-        <v>3.49</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="U3">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z3">
-        <v>3.62</v>
+        <v>5.31</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AB3">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AC3">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AF3">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG3">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.49</v>
       </c>
       <c r="P4">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="Q4">
+        <v>2.73</v>
+      </c>
+      <c r="R4">
+        <v>2.12</v>
+      </c>
+      <c r="S4">
+        <v>1.31</v>
+      </c>
+      <c r="T4">
+        <v>3.24</v>
+      </c>
+      <c r="U4">
+        <v>2.45</v>
+      </c>
+      <c r="V4">
+        <v>1.45</v>
+      </c>
+      <c r="W4">
+        <v>1.11</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.21</v>
+      </c>
+      <c r="Z4">
+        <v>3.62</v>
+      </c>
+      <c r="AA4">
+        <v>1.75</v>
+      </c>
+      <c r="AB4">
+        <v>1.95</v>
+      </c>
+      <c r="AC4">
+        <v>2.9</v>
+      </c>
+      <c r="AD4">
+        <v>1.36</v>
+      </c>
+      <c r="AE4">
+        <v>1.1</v>
+      </c>
+      <c r="AF4">
+        <v>1.62</v>
+      </c>
+      <c r="AG4">
         <v>2.18</v>
       </c>
-      <c r="R4">
-        <v>2.6</v>
-      </c>
-      <c r="S4">
-        <v>1.22</v>
-      </c>
-      <c r="T4">
-        <v>3.55</v>
-      </c>
-      <c r="U4">
-        <v>2.1</v>
-      </c>
-      <c r="V4">
-        <v>1.65</v>
-      </c>
-      <c r="W4">
-        <v>1.15</v>
-      </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
-        <v>1.13</v>
-      </c>
-      <c r="Z4">
-        <v>5.31</v>
-      </c>
-      <c r="AA4">
-        <v>1.44</v>
-      </c>
-      <c r="AB4">
-        <v>2.5</v>
-      </c>
-      <c r="AC4">
-        <v>2.15</v>
-      </c>
-      <c r="AD4">
-        <v>1.62</v>
-      </c>
-      <c r="AE4">
-        <v>1.23</v>
-      </c>
-      <c r="AF4">
-        <v>1.48</v>
-      </c>
-      <c r="AG4">
-        <v>2.5</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -3089,13 +3089,13 @@
         <v>2.67</v>
       </c>
       <c r="Q17">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R17">
         <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
         <v>2.8</v>
@@ -3104,10 +3104,10 @@
         <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3116,28 +3116,28 @@
         <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
         <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK17">
         <v>1.4</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
         <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
         <v>1.37</v>
@@ -674,22 +674,22 @@
         <v>2.68</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB2">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="AD2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG2">
         <v>1.8</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
         <v>1.5</v>
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="R3">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T3">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U3">
         <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,28 +834,28 @@
         <v>1.13</v>
       </c>
       <c r="Z3">
-        <v>5.31</v>
+        <v>5.75</v>
       </c>
       <c r="AA3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB3">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD3">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,43 +961,43 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="O4">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q4">
-        <v>2.73</v>
+        <v>2.52</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AA4">
         <v>1.75</v>
@@ -1009,16 +1009,16 @@
         <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
         <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="O5">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="P5">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Q5">
-        <v>5.9</v>
+        <v>4.94</v>
       </c>
       <c r="R5">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S5">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
         <v>1.14</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AB5">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AD5">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>2.78</v>
       </c>
       <c r="AK5">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="O11">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
         <v>3.26</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V11">
         <v>1.37</v>
@@ -2135,22 +2135,22 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
         <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
         <v>1.07</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK11">
         <v>1.44</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O12">
-        <v>5.46</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>7.95</v>
+        <v>6.7</v>
       </c>
       <c r="Q12">
         <v>1.67</v>
@@ -2280,16 +2280,16 @@
         <v>2.7</v>
       </c>
       <c r="S12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
         <v>3.85</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W12">
         <v>1.16</v>
@@ -2298,31 +2298,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.1</v>
+        <v>5.53</v>
       </c>
       <c r="AA12">
         <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AC12">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD12">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK12">
         <v>3.3</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O13">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R13">
         <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U13">
         <v>2.69</v>
@@ -2458,10 +2458,10 @@
         <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z13">
         <v>3.59</v>
@@ -2470,22 +2470,22 @@
         <v>1.92</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC13">
         <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="O14">
-        <v>3.74</v>
+        <v>4.52</v>
       </c>
       <c r="P14">
-        <v>4.36</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="S14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
         <v>1.48</v>
@@ -2624,31 +2624,31 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
         <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
         <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,22 +2754,22 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="O15">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="Q15">
         <v>4.2</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
         <v>3.18</v>
@@ -2778,25 +2778,25 @@
         <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AA15">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AC15">
         <v>2.75</v>
@@ -2811,7 +2811,7 @@
         <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AK15">
         <v>1.25</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="O16">
-        <v>4.26</v>
+        <v>4.4</v>
       </c>
       <c r="P16">
-        <v>4.68</v>
+        <v>5.25</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R16">
         <v>2.4</v>
@@ -2938,16 +2938,16 @@
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.18</v>
@@ -2956,25 +2956,25 @@
         <v>4.43</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AC16">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AD16">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
         <v>2.4</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.97</v>
+        <v>2.17</v>
       </c>
       <c r="O6">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P6">
-        <v>3.49</v>
+        <v>3</v>
       </c>
       <c r="Q6">
         <v>2.59</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S6">
         <v>1.28</v>
@@ -1323,7 +1323,7 @@
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.33</v>
+        <v>4.61</v>
       </c>
       <c r="AA6">
         <v>1.62</v>
@@ -1332,19 +1332,19 @@
         <v>2.24</v>
       </c>
       <c r="AC6">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD6">
         <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="O6">
         <v>3.65</v>
@@ -1317,13 +1317,13 @@
         <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.61</v>
+        <v>4.1</v>
       </c>
       <c r="AA6">
         <v>1.62</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
         <v>2.87</v>
       </c>
       <c r="Q2">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
         <v>2.62</v>
@@ -662,28 +662,28 @@
         <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AA2">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
         <v>4.11</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK2">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O3">
         <v>4.2</v>
       </c>
       <c r="P3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q3">
         <v>2.05</v>
@@ -813,13 +813,13 @@
         <v>2.72</v>
       </c>
       <c r="S3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V3">
         <v>1.67</v>
@@ -840,19 +840,19 @@
         <v>1.45</v>
       </c>
       <c r="AB3">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AC3">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD3">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AE3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG3">
         <v>2.47</v>
@@ -976,28 +976,28 @@
         <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
         <v>1.75</v>
@@ -1009,7 +1009,7 @@
         <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
         <v>1.15</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="O5">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="P5">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q5">
-        <v>4.94</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
         <v>2.2</v>
@@ -1157,16 +1157,16 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AC5">
         <v>2.4</v>
@@ -1175,13 +1175,13 @@
         <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
         <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U6">
         <v>2.3</v>
@@ -1323,7 +1323,7 @@
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA6">
         <v>1.62</v>
@@ -1338,7 +1338,7 @@
         <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
         <v>1.51</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
         <v>3.35</v>
@@ -2111,7 +2111,7 @@
         <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
         <v>1.97</v>
@@ -2120,13 +2120,13 @@
         <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U11">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
         <v>1.03</v>
@@ -2141,13 +2141,13 @@
         <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
         <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AD11">
         <v>1.25</v>
@@ -2175,7 +2175,7 @@
         <v>1.49</v>
       </c>
       <c r="AK11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O12">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="P12">
-        <v>6.7</v>
+        <v>8.25</v>
       </c>
       <c r="Q12">
         <v>1.67</v>
@@ -2298,7 +2298,7 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
         <v>5.53</v>
@@ -2307,10 +2307,10 @@
         <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AC12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
         <v>1.67</v>
@@ -2319,10 +2319,10 @@
         <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,16 +2431,16 @@
         <v>1.83</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q13">
         <v>2.31</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
         <v>3.59</v>
@@ -2470,16 +2470,16 @@
         <v>1.92</v>
       </c>
       <c r="AB13">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
         <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -2627,7 +2627,7 @@
         <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="AA14">
         <v>1.73</v>
@@ -2639,13 +2639,13 @@
         <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
         <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG14">
         <v>1.84</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,28 +2754,28 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P15">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
         <v>3.18</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V15">
         <v>1.49</v>
@@ -2787,31 +2787,31 @@
         <v>1.04</v>
       </c>
       <c r="Y15">
+        <v>1.18</v>
+      </c>
+      <c r="Z15">
+        <v>4.45</v>
+      </c>
+      <c r="AA15">
+        <v>1.65</v>
+      </c>
+      <c r="AB15">
+        <v>2.1</v>
+      </c>
+      <c r="AC15">
+        <v>2.7</v>
+      </c>
+      <c r="AD15">
+        <v>1.41</v>
+      </c>
+      <c r="AE15">
         <v>1.17</v>
       </c>
-      <c r="Z15">
-        <v>4.25</v>
-      </c>
-      <c r="AA15">
-        <v>1.7</v>
-      </c>
-      <c r="AB15">
-        <v>2.11</v>
-      </c>
-      <c r="AC15">
-        <v>2.75</v>
-      </c>
-      <c r="AD15">
-        <v>1.39</v>
-      </c>
-      <c r="AE15">
-        <v>1.12</v>
-      </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,37 +2917,37 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="P16">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q16">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R16">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.18</v>
@@ -2956,13 +2956,13 @@
         <v>4.43</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB16">
         <v>2.23</v>
       </c>
       <c r="AC16">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="AD16">
         <v>1.48</v>
@@ -2974,7 +2974,7 @@
         <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
         <v>2.4</v>
@@ -3089,10 +3089,10 @@
         <v>2.67</v>
       </c>
       <c r="Q17">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S17">
         <v>1.4</v>
@@ -3110,16 +3110,16 @@
         <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
         <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AA17">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
         <v>1.72</v>
@@ -3137,7 +3137,7 @@
         <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
         <v>1.4</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="O6">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q6">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="R6">
         <v>2.22</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
         <v>2.3</v>
@@ -1341,10 +1341,10 @@
         <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>2.67</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R17">
         <v>1.97</v>
@@ -3104,40 +3104,40 @@
         <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AA17">
         <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
         <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.36</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -3092,7 +3092,7 @@
         <v>3.42</v>
       </c>
       <c r="R17">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S17">
         <v>1.4</v>
@@ -3104,7 +3104,7 @@
         <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
         <v>1.07</v>
@@ -3119,7 +3119,7 @@
         <v>3.04</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB17">
         <v>1.75</v>
@@ -3128,7 +3128,7 @@
         <v>3.75</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
         <v>1.08</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P2">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q2">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R2">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="V2">
         <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z2">
         <v>2.8</v>
       </c>
       <c r="AA2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
         <v>1.56</v>
@@ -798,49 +798,49 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O3">
+        <v>4.33</v>
+      </c>
+      <c r="P3">
         <v>4.2</v>
       </c>
-      <c r="P3">
-        <v>3.7</v>
-      </c>
       <c r="Q3">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="R3">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="S3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U3">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
         <v>1.17</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z3">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AA3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB3">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC3">
         <v>2.15</v>
@@ -852,10 +852,10 @@
         <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="Q4">
         <v>2.52</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -991,10 +991,10 @@
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
         <v>3.8</v>
@@ -1003,22 +1003,22 @@
         <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD4">
         <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
         <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>1.4</v>
       </c>
       <c r="Q5">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="R5">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W5">
         <v>1.14</v>
@@ -1157,16 +1157,16 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>4.41</v>
       </c>
       <c r="AA5">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB5">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AC5">
         <v>2.4</v>
@@ -1181,7 +1181,7 @@
         <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         <v>2.22</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U6">
         <v>2.3</v>
@@ -1323,7 +1323,7 @@
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA6">
         <v>1.62</v>
@@ -1338,13 +1338,13 @@
         <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG6">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
         <v>1.62</v>
@@ -2102,61 +2102,61 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
         <v>1.97</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
         <v>1.03</v>
       </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z11">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC11">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD11">
         <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
         <v>1.91</v>
@@ -2175,7 +2175,7 @@
         <v>1.49</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="O12">
         <v>5.75</v>
       </c>
       <c r="P12">
-        <v>8.25</v>
+        <v>7.3</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R12">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S12">
         <v>1.2</v>
       </c>
       <c r="T12">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U12">
         <v>2.08</v>
@@ -2298,31 +2298,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z12">
-        <v>5.53</v>
+        <v>5.45</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AC12">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD12">
         <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>1.83</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="R13">
         <v>2.2</v>
@@ -2449,43 +2449,43 @@
         <v>2.99</v>
       </c>
       <c r="U13">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
+        <v>1.1</v>
+      </c>
+      <c r="X13">
         <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1</v>
       </c>
       <c r="Y13">
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="AA13">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="AD13">
         <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2594,28 +2594,28 @@
         <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="P14">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R14">
-        <v>2.57</v>
+        <v>2.23</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2624,22 +2624,22 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA14">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
         <v>1.13</v>
@@ -2648,7 +2648,7 @@
         <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,55 +2757,55 @@
         <v>3.9</v>
       </c>
       <c r="O15">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
-        <v>4.25</v>
+        <v>3.87</v>
       </c>
       <c r="R15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="U15">
         <v>2.39</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
         <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.62</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
         <v>1.24</v>
@@ -2920,22 +2920,22 @@
         <v>1.51</v>
       </c>
       <c r="O16">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P16">
-        <v>4.85</v>
+        <v>5.1</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U16">
         <v>2.35</v>
@@ -2944,25 +2944,25 @@
         <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AD16">
         <v>1.48</v>
@@ -2974,7 +2974,7 @@
         <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="Q6">
         <v>2.61</v>
@@ -1341,7 +1341,7 @@
         <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
         <v>2.37</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -3134,10 +3134,10 @@
         <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AK17">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="P2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
@@ -653,13 +653,13 @@
         <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -674,13 +674,13 @@
         <v>2.8</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
         <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="AD2">
         <v>1.18</v>
@@ -689,7 +689,7 @@
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG2">
         <v>1.85</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AK2">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O3">
         <v>4.33</v>
       </c>
       <c r="P3">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q3">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R3">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T3">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W3">
         <v>1.17</v>
@@ -852,10 +852,10 @@
         <v>1.25</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O4">
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="Q4">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="R4">
         <v>2.36</v>
@@ -982,34 +982,34 @@
         <v>2.99</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
         <v>2.72</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
         <v>1.1</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1133,7 +1133,7 @@
         <v>1.4</v>
       </c>
       <c r="Q5">
-        <v>6.1</v>
+        <v>5.03</v>
       </c>
       <c r="R5">
         <v>2.6</v>
@@ -1163,7 +1163,7 @@
         <v>4.41</v>
       </c>
       <c r="AA5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB5">
         <v>2.35</v>
@@ -1181,7 +1181,7 @@
         <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AK5">
         <v>1.07</v>
@@ -1341,10 +1341,10 @@
         <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG6">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,58 +2102,58 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
         <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q11">
+        <v>3.26</v>
+      </c>
+      <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11">
+        <v>1.4</v>
+      </c>
+      <c r="T11">
+        <v>2.88</v>
+      </c>
+      <c r="U11">
+        <v>2.73</v>
+      </c>
+      <c r="V11">
+        <v>1.38</v>
+      </c>
+      <c r="W11">
+        <v>1.04</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.3</v>
+      </c>
+      <c r="Z11">
         <v>3.1</v>
       </c>
-      <c r="R11">
-        <v>1.97</v>
-      </c>
-      <c r="S11">
-        <v>1.38</v>
-      </c>
-      <c r="T11">
-        <v>2.8</v>
-      </c>
-      <c r="U11">
-        <v>2.85</v>
-      </c>
-      <c r="V11">
-        <v>1.37</v>
-      </c>
-      <c r="W11">
-        <v>1.07</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.34</v>
-      </c>
-      <c r="Z11">
-        <v>2.93</v>
-      </c>
       <c r="AA11">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB11">
         <v>1.77</v>
       </c>
       <c r="AC11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD11">
         <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
         <v>1.75</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O12">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="P12">
         <v>7.3</v>
       </c>
       <c r="Q12">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S12">
         <v>1.2</v>
@@ -2286,43 +2286,43 @@
         <v>4</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
         <v>1.7</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA12">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AB12">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AC12">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AD12">
         <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2440,10 +2440,10 @@
         <v>2.4</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T13">
         <v>2.99</v>
@@ -2458,19 +2458,19 @@
         <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="AA13">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC13">
         <v>2.91</v>
@@ -2479,7 +2479,7 @@
         <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
@@ -2594,52 +2594,52 @@
         <v>1.44</v>
       </c>
       <c r="O14">
-        <v>4.35</v>
+        <v>4.52</v>
       </c>
       <c r="P14">
         <v>6.4</v>
       </c>
       <c r="Q14">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA14">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB14">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
         <v>1.13</v>
@@ -2648,7 +2648,7 @@
         <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,55 +2754,55 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q15">
-        <v>3.87</v>
+        <v>4.2</v>
       </c>
       <c r="R15">
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
         <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
         <v>1.13</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O16">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P16">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>2.4</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2953,28 +2953,28 @@
         <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="AA16">
         <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC16">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD16">
         <v>1.48</v>
       </c>
       <c r="AE16">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
         <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -3098,7 +3098,7 @@
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
         <v>2.8</v>
@@ -3128,7 +3128,7 @@
         <v>3.75</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
         <v>1.08</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
         <v>1.41</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -3089,13 +3089,13 @@
         <v>2.67</v>
       </c>
       <c r="Q17">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
         <v>2.75</v>
@@ -3104,7 +3104,7 @@
         <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.07</v>
@@ -3113,31 +3113,31 @@
         <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA17">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG17">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="Q2">
         <v>2.9</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
         <v>2.62</v>
       </c>
       <c r="U2">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA2">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB2">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
       <c r="AD2">
         <v>1.18</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O3">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="P3">
-        <v>4.15</v>
+        <v>4.95</v>
       </c>
       <c r="Q3">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="R3">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="S3">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W3">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z3">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA3">
         <v>1.44</v>
       </c>
       <c r="AB3">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AC3">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF3">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG3">
         <v>2.5</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
         <v>2.3</v>
@@ -961,46 +961,46 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="Q4">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R4">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
         <v>2.99</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
         <v>2.03</v>
@@ -1012,13 +1012,13 @@
         <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
         <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
         <v>1.75</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.3</v>
+        <v>6.85</v>
       </c>
       <c r="O5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P5">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Q5">
-        <v>5.03</v>
+        <v>6.1</v>
       </c>
       <c r="R5">
         <v>2.6</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
         <v>3.55</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,10 +1160,10 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB5">
         <v>2.35</v>
@@ -1175,10 +1175,10 @@
         <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
         <v>1.9</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AK5">
         <v>1.07</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O6">
         <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.98</v>
+        <v>3.19</v>
       </c>
       <c r="Q6">
         <v>2.61</v>
@@ -1308,22 +1308,22 @@
         <v>3.6</v>
       </c>
       <c r="U6">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
         <v>1.62</v>
@@ -1332,19 +1332,19 @@
         <v>2.24</v>
       </c>
       <c r="AC6">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD6">
         <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
         <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U11">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
         <v>1.04</v>
@@ -2135,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
         <v>1.99</v>
@@ -2147,19 +2147,19 @@
         <v>1.77</v>
       </c>
       <c r="AC11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O12">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="P12">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R12">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="S12">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,25 +2301,25 @@
         <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA12">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB12">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AC12">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD12">
         <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF12">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AG12">
         <v>1.84</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
         <v>3.3</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P13">
         <v>4.2</v>
@@ -2440,52 +2440,52 @@
         <v>2.4</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="U13">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AA13">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AB13">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC13">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,55 +2591,55 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O14">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q14">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U14">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>3.75</v>
+        <v>4.06</v>
       </c>
       <c r="AA14">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
         <v>1.13</v>
@@ -2648,7 +2648,7 @@
         <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
+        <v>3.75</v>
+      </c>
+      <c r="O15">
         <v>3.7</v>
       </c>
-      <c r="O15">
-        <v>3.8</v>
-      </c>
       <c r="P15">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q15">
         <v>4.2</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S15">
         <v>1.31</v>
@@ -2775,7 +2775,7 @@
         <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V15">
         <v>1.51</v>
@@ -2787,22 +2787,22 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
         <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE15">
         <v>1.13</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O16">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P16">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
         <v>2</v>
       </c>
       <c r="R16">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T16">
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
         <v>2.63</v>
       </c>
       <c r="AD16">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
         <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK16">
         <v>2.4</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q18">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P6">
         <v>3.19</v>
@@ -1323,19 +1323,19 @@
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA6">
         <v>1.62</v>
       </c>
       <c r="AB6">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AC6">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE6">
         <v>1.2</v>
@@ -1344,7 +1344,7 @@
         <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AK6">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="O8">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="P8">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
+        <v>1.55</v>
+      </c>
+      <c r="Q10">
+        <v>6.08</v>
+      </c>
+      <c r="R10">
+        <v>2.12</v>
+      </c>
+      <c r="S10">
+        <v>1.39</v>
+      </c>
+      <c r="T10">
+        <v>2.81</v>
+      </c>
+      <c r="U10">
+        <v>2.84</v>
+      </c>
+      <c r="V10">
         <v>1.38</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="O13">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q13">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T13">
         <v>3.15</v>
       </c>
       <c r="U13">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
+        <v>1.47</v>
+      </c>
+      <c r="W13">
+        <v>1.1</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.18</v>
+      </c>
+      <c r="Z13">
+        <v>4.06</v>
+      </c>
+      <c r="AA13">
+        <v>1.7</v>
+      </c>
+      <c r="AB13">
+        <v>2.07</v>
+      </c>
+      <c r="AC13">
+        <v>2.64</v>
+      </c>
+      <c r="AD13">
         <v>1.4</v>
       </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>1.22</v>
-      </c>
-      <c r="Z13">
-        <v>3.55</v>
-      </c>
-      <c r="AA13">
-        <v>1.86</v>
-      </c>
-      <c r="AB13">
-        <v>1.98</v>
-      </c>
-      <c r="AC13">
-        <v>3.05</v>
-      </c>
-      <c r="AD13">
-        <v>1.29</v>
-      </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>1.77</v>
+      </c>
+      <c r="O14">
+        <v>3.65</v>
+      </c>
+      <c r="P14">
+        <v>4.2</v>
+      </c>
+      <c r="Q14">
+        <v>2.4</v>
+      </c>
+      <c r="R14">
+        <v>2.2</v>
+      </c>
+      <c r="S14">
         <v>1.35</v>
-      </c>
-      <c r="O14">
-        <v>4.4</v>
-      </c>
-      <c r="P14">
-        <v>6.5</v>
-      </c>
-      <c r="Q14">
-        <v>1.83</v>
-      </c>
-      <c r="R14">
-        <v>2.43</v>
-      </c>
-      <c r="S14">
-        <v>1.31</v>
       </c>
       <c r="T14">
         <v>3.15</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V14">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
+        <v>1.05</v>
+      </c>
+      <c r="Y14">
+        <v>1.22</v>
+      </c>
+      <c r="Z14">
+        <v>3.55</v>
+      </c>
+      <c r="AA14">
+        <v>1.86</v>
+      </c>
+      <c r="AB14">
+        <v>1.98</v>
+      </c>
+      <c r="AC14">
+        <v>3.05</v>
+      </c>
+      <c r="AD14">
+        <v>1.29</v>
+      </c>
+      <c r="AE14">
         <v>1.1</v>
       </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.18</v>
-      </c>
-      <c r="Z14">
-        <v>4.06</v>
-      </c>
-      <c r="AA14">
-        <v>1.7</v>
-      </c>
-      <c r="AB14">
-        <v>2.07</v>
-      </c>
-      <c r="AC14">
-        <v>2.64</v>
-      </c>
-      <c r="AD14">
-        <v>1.4</v>
-      </c>
-      <c r="AE14">
-        <v>1.13</v>
-      </c>
       <c r="AF14">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R17">
         <v>2</v>
@@ -3098,37 +3098,37 @@
         <v>1.42</v>
       </c>
       <c r="T17">
+        <v>2.8</v>
+      </c>
+      <c r="U17">
         <v>2.75</v>
       </c>
-      <c r="U17">
-        <v>2.8</v>
-      </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC17">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
         <v>1.03</v>
@@ -3153,7 +3153,7 @@
         <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="Q2">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
         <v>3.22</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="AA2">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
         <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AK2">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,61 +801,61 @@
         <v>1.65</v>
       </c>
       <c r="O3">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="P3">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="Q3">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="R3">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U3">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="V3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.13</v>
       </c>
       <c r="Z3">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA3">
         <v>1.44</v>
       </c>
       <c r="AB3">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AC3">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AD3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF3">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="O4">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="Q4">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <v>2.45</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.07</v>
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA4">
         <v>1.8</v>
@@ -1006,10 +1006,10 @@
         <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
         <v>1.13</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
         <v>1.75</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="O5">
-        <v>4.9</v>
+        <v>4.98</v>
       </c>
       <c r="P5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q5">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T5">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="U5">
         <v>2.2</v>
@@ -1151,7 +1151,7 @@
         <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA5">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AC5">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD5">
         <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AK5">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         <v>2.01</v>
       </c>
       <c r="O6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="Q6">
         <v>2.61</v>
@@ -1320,7 +1320,7 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
         <v>4.4</v>
@@ -1332,7 +1332,7 @@
         <v>2.23</v>
       </c>
       <c r="AC6">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD6">
         <v>1.49</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
+        <v>1.55</v>
+      </c>
+      <c r="Q9">
+        <v>6.08</v>
+      </c>
+      <c r="R9">
+        <v>2.12</v>
+      </c>
+      <c r="S9">
+        <v>1.39</v>
+      </c>
+      <c r="T9">
+        <v>2.81</v>
+      </c>
+      <c r="U9">
+        <v>2.84</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.3</v>
+      </c>
+      <c r="Z9">
         <v>3.25</v>
       </c>
-      <c r="Q9">
-        <v>3.14</v>
-      </c>
-      <c r="R9">
-        <v>1.78</v>
-      </c>
-      <c r="S9">
-        <v>1.61</v>
-      </c>
-      <c r="T9">
-        <v>2.17</v>
-      </c>
-      <c r="U9">
-        <v>4.1</v>
-      </c>
-      <c r="V9">
-        <v>1.17</v>
-      </c>
-      <c r="W9">
-        <v>1.02</v>
-      </c>
-      <c r="X9">
+      <c r="AA9">
+        <v>2.07</v>
+      </c>
+      <c r="AB9">
+        <v>1.72</v>
+      </c>
+      <c r="AC9">
+        <v>3.6</v>
+      </c>
+      <c r="AD9">
+        <v>1.25</v>
+      </c>
+      <c r="AE9">
+        <v>1.06</v>
+      </c>
+      <c r="AF9">
+        <v>1.97</v>
+      </c>
+      <c r="AG9">
+        <v>1.73</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.2</v>
+      </c>
+      <c r="AK9">
         <v>1.07</v>
-      </c>
-      <c r="Y9">
-        <v>1.6</v>
-      </c>
-      <c r="Z9">
-        <v>2.19</v>
-      </c>
-      <c r="AA9">
-        <v>2.75</v>
-      </c>
-      <c r="AB9">
-        <v>1.4</v>
-      </c>
-      <c r="AC9">
-        <v>6</v>
-      </c>
-      <c r="AD9">
-        <v>1.06</v>
-      </c>
-      <c r="AE9">
-        <v>1.01</v>
-      </c>
-      <c r="AF9">
-        <v>2.28</v>
-      </c>
-      <c r="AG9">
-        <v>1.55</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.33</v>
-      </c>
-      <c r="AK9">
-        <v>1.49</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
+        <v>3.25</v>
+      </c>
+      <c r="Q10">
+        <v>3.14</v>
+      </c>
+      <c r="R10">
+        <v>1.78</v>
+      </c>
+      <c r="S10">
+        <v>1.61</v>
+      </c>
+      <c r="T10">
+        <v>2.17</v>
+      </c>
+      <c r="U10">
+        <v>4.1</v>
+      </c>
+      <c r="V10">
+        <v>1.17</v>
+      </c>
+      <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.07</v>
+      </c>
+      <c r="Y10">
+        <v>1.6</v>
+      </c>
+      <c r="Z10">
+        <v>2.19</v>
+      </c>
+      <c r="AA10">
+        <v>2.75</v>
+      </c>
+      <c r="AB10">
+        <v>1.4</v>
+      </c>
+      <c r="AC10">
+        <v>6</v>
+      </c>
+      <c r="AD10">
+        <v>1.06</v>
+      </c>
+      <c r="AE10">
+        <v>1.01</v>
+      </c>
+      <c r="AF10">
+        <v>2.28</v>
+      </c>
+      <c r="AG10">
         <v>1.55</v>
       </c>
-      <c r="Q10">
-        <v>6.08</v>
-      </c>
-      <c r="R10">
-        <v>2.12</v>
-      </c>
-      <c r="S10">
-        <v>1.39</v>
-      </c>
-      <c r="T10">
-        <v>2.81</v>
-      </c>
-      <c r="U10">
-        <v>2.84</v>
-      </c>
-      <c r="V10">
-        <v>1.38</v>
-      </c>
-      <c r="W10">
-        <v>1.05</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.3</v>
-      </c>
-      <c r="Z10">
-        <v>3.25</v>
-      </c>
-      <c r="AA10">
-        <v>2.07</v>
-      </c>
-      <c r="AB10">
-        <v>1.72</v>
-      </c>
-      <c r="AC10">
-        <v>3.6</v>
-      </c>
-      <c r="AD10">
-        <v>1.25</v>
-      </c>
-      <c r="AE10">
-        <v>1.06</v>
-      </c>
-      <c r="AF10">
-        <v>1.97</v>
-      </c>
-      <c r="AG10">
-        <v>1.73</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>2.62</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
         <v>2.5</v>
@@ -2117,16 +2117,16 @@
         <v>2.13</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
         <v>2.59</v>
       </c>
       <c r="U11">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="V11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
         <v>1.04</v>
@@ -2135,16 +2135,16 @@
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA11">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC11">
         <v>3.5</v>
@@ -2153,7 +2153,7 @@
         <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
         <v>1.8</v>
@@ -2268,31 +2268,31 @@
         <v>1.3</v>
       </c>
       <c r="O12">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="P12">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Q12">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R12">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="S12">
         <v>1.24</v>
       </c>
       <c r="T12">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
         <v>2</v>
       </c>
       <c r="V12">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W12">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,7 +2301,7 @@
         <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA12">
         <v>1.44</v>
@@ -2310,19 +2310,19 @@
         <v>2.75</v>
       </c>
       <c r="AC12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE12">
         <v>1.29</v>
       </c>
       <c r="AF12">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2434,28 +2434,28 @@
         <v>4.4</v>
       </c>
       <c r="P13">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q13">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="S13">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V13">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2464,16 +2464,16 @@
         <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
@@ -2485,7 +2485,7 @@
         <v>1.8</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,77 +2591,77 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O14">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="Q14">
         <v>2.4</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="U14">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AB14">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD14">
+        <v>1.28</v>
+      </c>
+      <c r="AE14">
+        <v>1.09</v>
+      </c>
+      <c r="AF14">
+        <v>1.8</v>
+      </c>
+      <c r="AG14">
+        <v>1.88</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.29</v>
-      </c>
-      <c r="AE14">
-        <v>1.1</v>
-      </c>
-      <c r="AF14">
-        <v>1.75</v>
-      </c>
-      <c r="AG14">
-        <v>1.97</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.22</v>
       </c>
       <c r="AK14">
         <v>1.91</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P15">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q15">
         <v>4.2</v>
       </c>
       <c r="R15">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
         <v>2.39</v>
@@ -2781,7 +2781,7 @@
         <v>1.51</v>
       </c>
       <c r="W15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2790,10 +2790,10 @@
         <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
         <v>2.15</v>
@@ -2802,10 +2802,10 @@
         <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
         <v>1.62</v>
@@ -2827,7 +2827,7 @@
         <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O16">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="P16">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R16">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
         <v>1.11</v>
@@ -2950,25 +2950,25 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC16">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD16">
         <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF16">
         <v>1.67</v>
@@ -2990,7 +2990,7 @@
         <v>1.13</v>
       </c>
       <c r="AK16">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P17">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="Q17">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R17">
         <v>2</v>
@@ -3110,13 +3110,13 @@
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA17">
         <v>2.05</v>
@@ -3125,16 +3125,16 @@
         <v>1.69</v>
       </c>
       <c r="AC17">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG17">
         <v>1.95</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="O18">
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
+        <v>2.25</v>
+      </c>
+      <c r="O7">
         <v>2.75</v>
       </c>
-      <c r="O7">
-        <v>2.55</v>
-      </c>
       <c r="P7">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>3.63</v>
+        <v>3.14</v>
       </c>
       <c r="R7">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="S7">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="T7">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="U7">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
         <v>1.02</v>
       </c>
       <c r="X7">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="Z7">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AA7">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AB7">
+        <v>1.4</v>
+      </c>
+      <c r="AC7">
+        <v>6</v>
+      </c>
+      <c r="AD7">
+        <v>1.06</v>
+      </c>
+      <c r="AE7">
+        <v>1.01</v>
+      </c>
+      <c r="AF7">
+        <v>2.28</v>
+      </c>
+      <c r="AG7">
+        <v>1.55</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.33</v>
       </c>
-      <c r="AC7">
-        <v>5.9</v>
-      </c>
-      <c r="AD7">
-        <v>1.07</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
-      <c r="AF7">
-        <v>2.3</v>
-      </c>
-      <c r="AG7">
-        <v>1.54</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.32</v>
-      </c>
       <c r="AK7">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O8">
         <v>2.55</v>
       </c>
       <c r="P8">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>3.82</v>
+        <v>3.63</v>
       </c>
       <c r="R8">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="S8">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y8">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="Z8">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="AA8">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB8">
+        <v>1.33</v>
+      </c>
+      <c r="AC8">
+        <v>5.9</v>
+      </c>
+      <c r="AD8">
+        <v>1.07</v>
+      </c>
+      <c r="AE8">
+        <v>1.03</v>
+      </c>
+      <c r="AF8">
+        <v>2.3</v>
+      </c>
+      <c r="AG8">
+        <v>1.54</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.32</v>
+      </c>
+      <c r="AK8">
         <v>1.4</v>
-      </c>
-      <c r="AC8">
-        <v>5.35</v>
-      </c>
-      <c r="AD8">
-        <v>1.09</v>
-      </c>
-      <c r="AE8">
-        <v>1.02</v>
-      </c>
-      <c r="AF8">
-        <v>2.15</v>
-      </c>
-      <c r="AG8">
-        <v>1.61</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.38</v>
-      </c>
-      <c r="AK8">
-        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>5.5</v>
+        <v>2.85</v>
       </c>
       <c r="O9">
+        <v>2.55</v>
+      </c>
+      <c r="P9">
+        <v>2.75</v>
+      </c>
+      <c r="Q9">
+        <v>3.82</v>
+      </c>
+      <c r="R9">
+        <v>1.72</v>
+      </c>
+      <c r="S9">
+        <v>1.61</v>
+      </c>
+      <c r="T9">
+        <v>2.25</v>
+      </c>
+      <c r="U9">
         <v>3.8</v>
       </c>
-      <c r="P9">
-        <v>1.55</v>
-      </c>
-      <c r="Q9">
-        <v>6.08</v>
-      </c>
-      <c r="R9">
-        <v>2.12</v>
-      </c>
-      <c r="S9">
-        <v>1.39</v>
-      </c>
-      <c r="T9">
-        <v>2.81</v>
-      </c>
-      <c r="U9">
-        <v>2.84</v>
-      </c>
       <c r="V9">
+        <v>1.2</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1.09</v>
+      </c>
+      <c r="Y9">
+        <v>1.56</v>
+      </c>
+      <c r="Z9">
+        <v>2.37</v>
+      </c>
+      <c r="AA9">
+        <v>2.75</v>
+      </c>
+      <c r="AB9">
+        <v>1.4</v>
+      </c>
+      <c r="AC9">
+        <v>5.35</v>
+      </c>
+      <c r="AD9">
+        <v>1.09</v>
+      </c>
+      <c r="AE9">
+        <v>1.02</v>
+      </c>
+      <c r="AF9">
+        <v>2.15</v>
+      </c>
+      <c r="AG9">
+        <v>1.61</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.38</v>
       </c>
-      <c r="W9">
-        <v>1.05</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.3</v>
-      </c>
-      <c r="Z9">
-        <v>3.25</v>
-      </c>
-      <c r="AA9">
-        <v>2.07</v>
-      </c>
-      <c r="AB9">
-        <v>1.72</v>
-      </c>
-      <c r="AC9">
-        <v>3.6</v>
-      </c>
-      <c r="AD9">
-        <v>1.25</v>
-      </c>
-      <c r="AE9">
-        <v>1.06</v>
-      </c>
-      <c r="AF9">
-        <v>1.97</v>
-      </c>
-      <c r="AG9">
-        <v>1.73</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.2</v>
-      </c>
       <c r="AK9">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
+        <v>1.55</v>
+      </c>
+      <c r="Q10">
+        <v>6.08</v>
+      </c>
+      <c r="R10">
+        <v>2.12</v>
+      </c>
+      <c r="S10">
+        <v>1.39</v>
+      </c>
+      <c r="T10">
+        <v>2.81</v>
+      </c>
+      <c r="U10">
+        <v>2.84</v>
+      </c>
+      <c r="V10">
+        <v>1.38</v>
+      </c>
+      <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>1.3</v>
+      </c>
+      <c r="Z10">
         <v>3.25</v>
       </c>
-      <c r="Q10">
-        <v>3.14</v>
-      </c>
-      <c r="R10">
-        <v>1.78</v>
-      </c>
-      <c r="S10">
-        <v>1.61</v>
-      </c>
-      <c r="T10">
-        <v>2.17</v>
-      </c>
-      <c r="U10">
-        <v>4.1</v>
-      </c>
-      <c r="V10">
-        <v>1.17</v>
-      </c>
-      <c r="W10">
-        <v>1.02</v>
-      </c>
-      <c r="X10">
+      <c r="AA10">
+        <v>2.07</v>
+      </c>
+      <c r="AB10">
+        <v>1.72</v>
+      </c>
+      <c r="AC10">
+        <v>3.6</v>
+      </c>
+      <c r="AD10">
+        <v>1.25</v>
+      </c>
+      <c r="AE10">
+        <v>1.06</v>
+      </c>
+      <c r="AF10">
+        <v>1.97</v>
+      </c>
+      <c r="AG10">
+        <v>1.73</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.2</v>
+      </c>
+      <c r="AK10">
         <v>1.07</v>
-      </c>
-      <c r="Y10">
-        <v>1.6</v>
-      </c>
-      <c r="Z10">
-        <v>2.19</v>
-      </c>
-      <c r="AA10">
-        <v>2.75</v>
-      </c>
-      <c r="AB10">
-        <v>1.4</v>
-      </c>
-      <c r="AC10">
-        <v>6</v>
-      </c>
-      <c r="AD10">
-        <v>1.06</v>
-      </c>
-      <c r="AE10">
-        <v>1.01</v>
-      </c>
-      <c r="AF10">
-        <v>2.28</v>
-      </c>
-      <c r="AG10">
-        <v>1.55</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.33</v>
-      </c>
-      <c r="AK10">
-        <v>1.49</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="O7">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="P7">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q7">
-        <v>3.14</v>
+        <v>3.63</v>
       </c>
       <c r="R7">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="S7">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="T7">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
         <v>1.02</v>
       </c>
       <c r="X7">
+        <v>1.11</v>
+      </c>
+      <c r="Y7">
+        <v>1.64</v>
+      </c>
+      <c r="Z7">
+        <v>2.12</v>
+      </c>
+      <c r="AA7">
+        <v>3.25</v>
+      </c>
+      <c r="AB7">
+        <v>1.33</v>
+      </c>
+      <c r="AC7">
+        <v>5.9</v>
+      </c>
+      <c r="AD7">
         <v>1.07</v>
       </c>
-      <c r="Y7">
-        <v>1.6</v>
-      </c>
-      <c r="Z7">
-        <v>2.19</v>
-      </c>
-      <c r="AA7">
-        <v>2.75</v>
-      </c>
-      <c r="AB7">
+      <c r="AE7">
+        <v>1.03</v>
+      </c>
+      <c r="AF7">
+        <v>2.3</v>
+      </c>
+      <c r="AG7">
+        <v>1.54</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.32</v>
+      </c>
+      <c r="AK7">
         <v>1.4</v>
-      </c>
-      <c r="AC7">
-        <v>6</v>
-      </c>
-      <c r="AD7">
-        <v>1.06</v>
-      </c>
-      <c r="AE7">
-        <v>1.01</v>
-      </c>
-      <c r="AF7">
-        <v>2.28</v>
-      </c>
-      <c r="AG7">
-        <v>1.55</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.33</v>
-      </c>
-      <c r="AK7">
-        <v>1.49</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O8">
         <v>2.55</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q8">
-        <v>3.63</v>
+        <v>3.82</v>
       </c>
       <c r="R8">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="S8">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="T8">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="U8">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="V8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1.09</v>
+      </c>
+      <c r="Y8">
+        <v>1.56</v>
+      </c>
+      <c r="Z8">
+        <v>2.37</v>
+      </c>
+      <c r="AA8">
+        <v>2.75</v>
+      </c>
+      <c r="AB8">
+        <v>1.4</v>
+      </c>
+      <c r="AC8">
+        <v>5.35</v>
+      </c>
+      <c r="AD8">
+        <v>1.09</v>
+      </c>
+      <c r="AE8">
         <v>1.02</v>
       </c>
-      <c r="X8">
-        <v>1.11</v>
-      </c>
-      <c r="Y8">
-        <v>1.64</v>
-      </c>
-      <c r="Z8">
-        <v>2.12</v>
-      </c>
-      <c r="AA8">
-        <v>3.25</v>
-      </c>
-      <c r="AB8">
+      <c r="AF8">
+        <v>2.15</v>
+      </c>
+      <c r="AG8">
+        <v>1.61</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.38</v>
+      </c>
+      <c r="AK8">
         <v>1.33</v>
-      </c>
-      <c r="AC8">
-        <v>5.9</v>
-      </c>
-      <c r="AD8">
-        <v>1.07</v>
-      </c>
-      <c r="AE8">
-        <v>1.03</v>
-      </c>
-      <c r="AF8">
-        <v>2.3</v>
-      </c>
-      <c r="AG8">
-        <v>1.54</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.32</v>
-      </c>
-      <c r="AK8">
-        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.85</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="Q9">
-        <v>3.82</v>
+        <v>6.08</v>
       </c>
       <c r="R9">
+        <v>2.12</v>
+      </c>
+      <c r="S9">
+        <v>1.39</v>
+      </c>
+      <c r="T9">
+        <v>2.81</v>
+      </c>
+      <c r="U9">
+        <v>2.84</v>
+      </c>
+      <c r="V9">
+        <v>1.38</v>
+      </c>
+      <c r="W9">
+        <v>1.05</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.3</v>
+      </c>
+      <c r="Z9">
+        <v>3.25</v>
+      </c>
+      <c r="AA9">
+        <v>2.07</v>
+      </c>
+      <c r="AB9">
         <v>1.72</v>
       </c>
-      <c r="S9">
-        <v>1.61</v>
-      </c>
-      <c r="T9">
-        <v>2.25</v>
-      </c>
-      <c r="U9">
-        <v>3.8</v>
-      </c>
-      <c r="V9">
+      <c r="AC9">
+        <v>3.6</v>
+      </c>
+      <c r="AD9">
+        <v>1.25</v>
+      </c>
+      <c r="AE9">
+        <v>1.06</v>
+      </c>
+      <c r="AF9">
+        <v>1.97</v>
+      </c>
+      <c r="AG9">
+        <v>1.73</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.2</v>
       </c>
-      <c r="W9">
-        <v>1.01</v>
-      </c>
-      <c r="X9">
-        <v>1.09</v>
-      </c>
-      <c r="Y9">
-        <v>1.56</v>
-      </c>
-      <c r="Z9">
-        <v>2.37</v>
-      </c>
-      <c r="AA9">
-        <v>2.75</v>
-      </c>
-      <c r="AB9">
-        <v>1.4</v>
-      </c>
-      <c r="AC9">
-        <v>5.35</v>
-      </c>
-      <c r="AD9">
-        <v>1.09</v>
-      </c>
-      <c r="AE9">
-        <v>1.02</v>
-      </c>
-      <c r="AF9">
-        <v>2.15</v>
-      </c>
-      <c r="AG9">
-        <v>1.61</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.38</v>
-      </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
+        <v>3.25</v>
+      </c>
+      <c r="Q10">
+        <v>3.14</v>
+      </c>
+      <c r="R10">
+        <v>1.78</v>
+      </c>
+      <c r="S10">
+        <v>1.61</v>
+      </c>
+      <c r="T10">
+        <v>2.17</v>
+      </c>
+      <c r="U10">
+        <v>4.1</v>
+      </c>
+      <c r="V10">
+        <v>1.17</v>
+      </c>
+      <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.07</v>
+      </c>
+      <c r="Y10">
+        <v>1.6</v>
+      </c>
+      <c r="Z10">
+        <v>2.19</v>
+      </c>
+      <c r="AA10">
+        <v>2.75</v>
+      </c>
+      <c r="AB10">
+        <v>1.4</v>
+      </c>
+      <c r="AC10">
+        <v>6</v>
+      </c>
+      <c r="AD10">
+        <v>1.06</v>
+      </c>
+      <c r="AE10">
+        <v>1.01</v>
+      </c>
+      <c r="AF10">
+        <v>2.28</v>
+      </c>
+      <c r="AG10">
         <v>1.55</v>
       </c>
-      <c r="Q10">
-        <v>6.08</v>
-      </c>
-      <c r="R10">
-        <v>2.12</v>
-      </c>
-      <c r="S10">
-        <v>1.39</v>
-      </c>
-      <c r="T10">
-        <v>2.81</v>
-      </c>
-      <c r="U10">
-        <v>2.84</v>
-      </c>
-      <c r="V10">
-        <v>1.38</v>
-      </c>
-      <c r="W10">
-        <v>1.05</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.3</v>
-      </c>
-      <c r="Z10">
-        <v>3.25</v>
-      </c>
-      <c r="AA10">
-        <v>2.07</v>
-      </c>
-      <c r="AB10">
-        <v>1.72</v>
-      </c>
-      <c r="AC10">
-        <v>3.6</v>
-      </c>
-      <c r="AD10">
-        <v>1.25</v>
-      </c>
-      <c r="AE10">
-        <v>1.06</v>
-      </c>
-      <c r="AF10">
-        <v>1.97</v>
-      </c>
-      <c r="AG10">
-        <v>1.73</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.07</v>
+        <v>1.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="O17">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="Q17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
         <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
         <v>2.75</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>1.06</v>
@@ -3119,10 +3119,10 @@
         <v>3</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
         <v>3.8</v>
@@ -3131,10 +3131,10 @@
         <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
         <v>1.95</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O2">
+        <v>3.05</v>
+      </c>
+      <c r="P2">
+        <v>2.7</v>
+      </c>
+      <c r="Q2">
         <v>3.3</v>
       </c>
-      <c r="P2">
-        <v>2.85</v>
-      </c>
-      <c r="Q2">
-        <v>3.1</v>
-      </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="U2">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
         <v>1.05</v>
       </c>
-      <c r="X2">
-        <v>1.07</v>
-      </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z2">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AA2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
         <v>1.57</v>
       </c>
       <c r="AC2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD2">
         <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK2">
         <v>1.5</v>
@@ -801,61 +801,61 @@
         <v>1.65</v>
       </c>
       <c r="O3">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="P3">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="Q3">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="S3">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U3">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="V3">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="W3">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z3">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB3">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC3">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AD3">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AE3">
         <v>1.28</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="Q4">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="U4">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
         <v>3.7</v>
       </c>
       <c r="AA4">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,77 +1124,77 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="O5">
         <v>4.98</v>
       </c>
       <c r="P5">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q5">
         <v>6</v>
       </c>
       <c r="R5">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="S5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>1.51</v>
       </c>
       <c r="AB5">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AD5">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE5">
+        <v>1.22</v>
+      </c>
+      <c r="AF5">
+        <v>1.79</v>
+      </c>
+      <c r="AG5">
+        <v>1.92</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.2</v>
-      </c>
-      <c r="AF5">
-        <v>1.75</v>
-      </c>
-      <c r="AG5">
-        <v>1.95</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>2.91</v>
       </c>
       <c r="AK5">
         <v>1.1</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
+        <v>2.31</v>
+      </c>
+      <c r="O7">
+        <v>2.72</v>
+      </c>
+      <c r="P7">
+        <v>2.65</v>
+      </c>
+      <c r="Q7">
+        <v>3.65</v>
+      </c>
+      <c r="R7">
+        <v>1.72</v>
+      </c>
+      <c r="S7">
+        <v>1.62</v>
+      </c>
+      <c r="T7">
+        <v>2.24</v>
+      </c>
+      <c r="U7">
+        <v>4.1</v>
+      </c>
+      <c r="V7">
+        <v>1.2</v>
+      </c>
+      <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
+        <v>1.1</v>
+      </c>
+      <c r="Y7">
+        <v>1.55</v>
+      </c>
+      <c r="Z7">
+        <v>2.29</v>
+      </c>
+      <c r="AA7">
         <v>2.75</v>
       </c>
-      <c r="O7">
-        <v>2.55</v>
-      </c>
-      <c r="P7">
-        <v>2.8</v>
-      </c>
-      <c r="Q7">
-        <v>3.63</v>
-      </c>
-      <c r="R7">
-        <v>1.82</v>
-      </c>
-      <c r="S7">
-        <v>1.69</v>
-      </c>
-      <c r="T7">
-        <v>2.04</v>
-      </c>
-      <c r="U7">
-        <v>4.33</v>
-      </c>
-      <c r="V7">
-        <v>1.18</v>
-      </c>
-      <c r="W7">
+      <c r="AB7">
+        <v>1.4</v>
+      </c>
+      <c r="AC7">
+        <v>6.5</v>
+      </c>
+      <c r="AD7">
+        <v>1.12</v>
+      </c>
+      <c r="AE7">
         <v>1.02</v>
       </c>
-      <c r="X7">
-        <v>1.11</v>
-      </c>
-      <c r="Y7">
-        <v>1.64</v>
-      </c>
-      <c r="Z7">
-        <v>2.12</v>
-      </c>
-      <c r="AA7">
-        <v>3.25</v>
-      </c>
-      <c r="AB7">
-        <v>1.33</v>
-      </c>
-      <c r="AC7">
-        <v>5.9</v>
-      </c>
-      <c r="AD7">
-        <v>1.07</v>
-      </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
       <c r="AF7">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG7">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="P8">
         <v>2.75</v>
       </c>
       <c r="Q8">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="S8">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="T8">
         <v>2.25</v>
       </c>
       <c r="U8">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="Z8">
-        <v>2.37</v>
+        <v>2.14</v>
       </c>
       <c r="AA8">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB8">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC8">
-        <v>5.35</v>
+        <v>5.9</v>
       </c>
       <c r="AD8">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG8">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q9">
-        <v>6.08</v>
+        <v>6.18</v>
       </c>
       <c r="R9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
         <v>1.38</v>
@@ -1809,16 +1809,16 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA9">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
         <v>3.6</v>
@@ -1830,10 +1830,10 @@
         <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
         <v>1.07</v>
@@ -1939,37 +1939,37 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="O10">
         <v>2.75</v>
       </c>
       <c r="P10">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="Q10">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S10">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T10">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U10">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="V10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y10">
         <v>1.6</v>
@@ -1978,10 +1978,10 @@
         <v>2.19</v>
       </c>
       <c r="AA10">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB10">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1996,7 +1996,7 @@
         <v>2.28</v>
       </c>
       <c r="AG10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q11">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
         <v>2.59</v>
       </c>
       <c r="U11">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="V11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB11">
+        <v>1.74</v>
+      </c>
+      <c r="AC11">
+        <v>3.55</v>
+      </c>
+      <c r="AD11">
+        <v>1.24</v>
+      </c>
+      <c r="AE11">
+        <v>1.05</v>
+      </c>
+      <c r="AF11">
         <v>1.73</v>
       </c>
-      <c r="AC11">
-        <v>3.5</v>
-      </c>
-      <c r="AD11">
-        <v>1.28</v>
-      </c>
-      <c r="AE11">
-        <v>1.08</v>
-      </c>
-      <c r="AF11">
-        <v>1.8</v>
-      </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O12">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q12">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R12">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="S12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
         <v>3.75</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V12">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB12">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE12">
         <v>1.29</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK12">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="O13">
-        <v>4.4</v>
+        <v>4.58</v>
       </c>
       <c r="P13">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R13">
-        <v>2.59</v>
+        <v>2.22</v>
       </c>
       <c r="S13">
         <v>1.3</v>
@@ -2455,25 +2455,25 @@
         <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.23</v>
+        <v>4.24</v>
       </c>
       <c r="AA13">
         <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
@@ -2482,10 +2482,10 @@
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P14">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R14">
         <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
         <v>1.04</v>
@@ -2624,31 +2624,31 @@
         <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC14">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
         <v>1.8</v>
       </c>
       <c r="AG14">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="O15">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U15">
         <v>2.39</v>
@@ -2781,37 +2781,37 @@
         <v>1.51</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
         <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK15">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,31 +2920,31 @@
         <v>1.4</v>
       </c>
       <c r="O16">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>5.4</v>
+        <v>7.1</v>
       </c>
       <c r="Q16">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R16">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U16">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2956,41 +2956,41 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB16">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC16">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE16">
+        <v>1.2</v>
+      </c>
+      <c r="AF16">
+        <v>1.75</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.18</v>
       </c>
-      <c r="AF16">
-        <v>1.67</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.13</v>
-      </c>
       <c r="AK16">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="U17">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
         <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AA17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
         <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
         <v>2.35</v>
@@ -1314,25 +1314,25 @@
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
         <v>1.62</v>
       </c>
       <c r="AB6">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD6">
         <v>1.49</v>
@@ -1344,7 +1344,7 @@
         <v>1.52</v>
       </c>
       <c r="AG6">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AK6">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.31</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
-        <v>3.65</v>
+        <v>6.18</v>
       </c>
       <c r="R7">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="S7">
+        <v>1.41</v>
+      </c>
+      <c r="T7">
+        <v>2.62</v>
+      </c>
+      <c r="U7">
+        <v>2.73</v>
+      </c>
+      <c r="V7">
+        <v>1.38</v>
+      </c>
+      <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.29</v>
+      </c>
+      <c r="Z7">
+        <v>3.3</v>
+      </c>
+      <c r="AA7">
+        <v>1.94</v>
+      </c>
+      <c r="AB7">
+        <v>1.76</v>
+      </c>
+      <c r="AC7">
+        <v>3.6</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.06</v>
+      </c>
+      <c r="AF7">
+        <v>2.1</v>
+      </c>
+      <c r="AG7">
         <v>1.62</v>
       </c>
-      <c r="T7">
-        <v>2.24</v>
-      </c>
-      <c r="U7">
-        <v>4.1</v>
-      </c>
-      <c r="V7">
-        <v>1.2</v>
-      </c>
-      <c r="W7">
-        <v>1.03</v>
-      </c>
-      <c r="X7">
-        <v>1.1</v>
-      </c>
-      <c r="Y7">
-        <v>1.55</v>
-      </c>
-      <c r="Z7">
-        <v>2.29</v>
-      </c>
-      <c r="AA7">
-        <v>2.75</v>
-      </c>
-      <c r="AB7">
-        <v>1.4</v>
-      </c>
-      <c r="AC7">
-        <v>6.5</v>
-      </c>
-      <c r="AD7">
-        <v>1.12</v>
-      </c>
-      <c r="AE7">
-        <v>1.02</v>
-      </c>
-      <c r="AF7">
-        <v>2.15</v>
-      </c>
-      <c r="AG7">
-        <v>1.67</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O8">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="P8">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R8">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="S8">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="V8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z8">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AA8">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB8">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC8">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AD8">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>2.45</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="P9">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q9">
-        <v>6.18</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
+        <v>1.83</v>
+      </c>
+      <c r="S9">
+        <v>1.64</v>
+      </c>
+      <c r="T9">
+        <v>2.25</v>
+      </c>
+      <c r="U9">
+        <v>4.33</v>
+      </c>
+      <c r="V9">
+        <v>1.18</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.1</v>
+      </c>
+      <c r="Y9">
+        <v>1.63</v>
+      </c>
+      <c r="Z9">
         <v>2.14</v>
       </c>
-      <c r="S9">
-        <v>1.41</v>
-      </c>
-      <c r="T9">
-        <v>2.62</v>
-      </c>
-      <c r="U9">
-        <v>2.73</v>
-      </c>
-      <c r="V9">
-        <v>1.38</v>
-      </c>
-      <c r="W9">
-        <v>1.05</v>
-      </c>
-      <c r="X9">
+      <c r="AA9">
+        <v>2.85</v>
+      </c>
+      <c r="AB9">
+        <v>1.34</v>
+      </c>
+      <c r="AC9">
+        <v>5.9</v>
+      </c>
+      <c r="AD9">
+        <v>1.07</v>
+      </c>
+      <c r="AE9">
         <v>1.03</v>
       </c>
-      <c r="Y9">
-        <v>1.29</v>
-      </c>
-      <c r="Z9">
-        <v>3.3</v>
-      </c>
-      <c r="AA9">
-        <v>1.94</v>
-      </c>
-      <c r="AB9">
-        <v>1.76</v>
-      </c>
-      <c r="AC9">
-        <v>3.6</v>
-      </c>
-      <c r="AD9">
-        <v>1.25</v>
-      </c>
-      <c r="AE9">
-        <v>1.06</v>
-      </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q18">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="R18">
+        <v>2.01</v>
+      </c>
+      <c r="S18">
+        <v>1.39</v>
+      </c>
+      <c r="T18">
+        <v>2.66</v>
+      </c>
+      <c r="U18">
+        <v>2.8</v>
+      </c>
+      <c r="V18">
+        <v>1.36</v>
+      </c>
+      <c r="W18">
+        <v>1.06</v>
+      </c>
+      <c r="X18">
+        <v>1.05</v>
+      </c>
+      <c r="Y18">
+        <v>1.27</v>
+      </c>
+      <c r="Z18">
+        <v>3.25</v>
+      </c>
+      <c r="AA18">
         <v>1.98</v>
       </c>
-      <c r="S18">
-        <v>1.41</v>
-      </c>
-      <c r="T18">
-        <v>2.59</v>
-      </c>
-      <c r="U18">
-        <v>2.96</v>
-      </c>
-      <c r="V18">
-        <v>1.32</v>
-      </c>
-      <c r="W18">
-        <v>1.05</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
-      </c>
-      <c r="Y18">
+      <c r="AB18">
+        <v>1.78</v>
+      </c>
+      <c r="AC18">
+        <v>3.42</v>
+      </c>
+      <c r="AD18">
         <v>1.29</v>
       </c>
-      <c r="Z18">
-        <v>3.2</v>
-      </c>
-      <c r="AA18">
-        <v>2.03</v>
-      </c>
-      <c r="AB18">
-        <v>1.7</v>
-      </c>
-      <c r="AC18">
-        <v>3.58</v>
-      </c>
-      <c r="AD18">
-        <v>1.22</v>
-      </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG18">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>2.31</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q7">
-        <v>6.18</v>
+        <v>3.65</v>
       </c>
       <c r="R7">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="S7">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="T7">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="U7">
-        <v>2.73</v>
+        <v>4.1</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="Z7">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="AA7">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AB7">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AC7">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG7">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.31</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="Q8">
-        <v>3.65</v>
+        <v>6.18</v>
       </c>
       <c r="R8">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
+        <v>1.41</v>
+      </c>
+      <c r="T8">
+        <v>2.62</v>
+      </c>
+      <c r="U8">
+        <v>2.73</v>
+      </c>
+      <c r="V8">
+        <v>1.38</v>
+      </c>
+      <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>1.29</v>
+      </c>
+      <c r="Z8">
+        <v>3.3</v>
+      </c>
+      <c r="AA8">
+        <v>1.94</v>
+      </c>
+      <c r="AB8">
+        <v>1.76</v>
+      </c>
+      <c r="AC8">
+        <v>3.6</v>
+      </c>
+      <c r="AD8">
+        <v>1.25</v>
+      </c>
+      <c r="AE8">
+        <v>1.06</v>
+      </c>
+      <c r="AF8">
+        <v>2.1</v>
+      </c>
+      <c r="AG8">
         <v>1.62</v>
       </c>
-      <c r="T8">
-        <v>2.24</v>
-      </c>
-      <c r="U8">
-        <v>4.1</v>
-      </c>
-      <c r="V8">
-        <v>1.2</v>
-      </c>
-      <c r="W8">
-        <v>1.03</v>
-      </c>
-      <c r="X8">
-        <v>1.1</v>
-      </c>
-      <c r="Y8">
-        <v>1.55</v>
-      </c>
-      <c r="Z8">
-        <v>2.29</v>
-      </c>
-      <c r="AA8">
-        <v>2.75</v>
-      </c>
-      <c r="AB8">
-        <v>1.4</v>
-      </c>
-      <c r="AC8">
-        <v>6.5</v>
-      </c>
-      <c r="AD8">
-        <v>1.12</v>
-      </c>
-      <c r="AE8">
-        <v>1.02</v>
-      </c>
-      <c r="AF8">
-        <v>2.15</v>
-      </c>
-      <c r="AG8">
-        <v>1.67</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q8">
-        <v>6.18</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
+        <v>1.83</v>
+      </c>
+      <c r="S8">
+        <v>1.64</v>
+      </c>
+      <c r="T8">
+        <v>2.25</v>
+      </c>
+      <c r="U8">
+        <v>4.33</v>
+      </c>
+      <c r="V8">
+        <v>1.18</v>
+      </c>
+      <c r="W8">
+        <v>1.02</v>
+      </c>
+      <c r="X8">
+        <v>1.1</v>
+      </c>
+      <c r="Y8">
+        <v>1.63</v>
+      </c>
+      <c r="Z8">
         <v>2.14</v>
       </c>
-      <c r="S8">
-        <v>1.41</v>
-      </c>
-      <c r="T8">
-        <v>2.62</v>
-      </c>
-      <c r="U8">
-        <v>2.73</v>
-      </c>
-      <c r="V8">
-        <v>1.38</v>
-      </c>
-      <c r="W8">
-        <v>1.05</v>
-      </c>
-      <c r="X8">
+      <c r="AA8">
+        <v>2.85</v>
+      </c>
+      <c r="AB8">
+        <v>1.34</v>
+      </c>
+      <c r="AC8">
+        <v>5.9</v>
+      </c>
+      <c r="AD8">
+        <v>1.07</v>
+      </c>
+      <c r="AE8">
         <v>1.03</v>
       </c>
-      <c r="Y8">
-        <v>1.29</v>
-      </c>
-      <c r="Z8">
-        <v>3.3</v>
-      </c>
-      <c r="AA8">
-        <v>1.94</v>
-      </c>
-      <c r="AB8">
-        <v>1.76</v>
-      </c>
-      <c r="AC8">
-        <v>3.6</v>
-      </c>
-      <c r="AD8">
-        <v>1.25</v>
-      </c>
-      <c r="AE8">
-        <v>1.06</v>
-      </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.45</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>6.18</v>
       </c>
       <c r="R9">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>4.33</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA9">
-        <v>2.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB9">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD9">
+        <v>1.25</v>
+      </c>
+      <c r="AE9">
+        <v>1.06</v>
+      </c>
+      <c r="AF9">
+        <v>2.1</v>
+      </c>
+      <c r="AG9">
+        <v>1.62</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.19</v>
+      </c>
+      <c r="AK9">
         <v>1.07</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
-      <c r="AF9">
-        <v>2.3</v>
-      </c>
-      <c r="AG9">
-        <v>1.54</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.36</v>
-      </c>
-      <c r="AK9">
-        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,68 +631,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.35</v>
+        <v>2.91</v>
       </c>
       <c r="O2">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="P2">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T2">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="U2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
         <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y2">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z2">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -701,41 +701,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AJ2">
+        <v>1.36</v>
+      </c>
+      <c r="AK2">
         <v>1.4</v>
       </c>
-      <c r="AK2">
-        <v>1.5</v>
-      </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="O3">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P3">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R3">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>5.5</v>
+        <v>4.96</v>
       </c>
       <c r="AA3">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AB3">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AC3">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="AD3">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AE3">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,118 +950,118 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R4">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.18</v>
+      </c>
+      <c r="Z4">
+        <v>4.1</v>
+      </c>
+      <c r="AA4">
+        <v>1.57</v>
+      </c>
+      <c r="AB4">
+        <v>2.29</v>
+      </c>
+      <c r="AC4">
+        <v>2.5</v>
+      </c>
+      <c r="AD4">
+        <v>1.45</v>
+      </c>
+      <c r="AE4">
+        <v>1.17</v>
+      </c>
+      <c r="AF4">
+        <v>1.55</v>
+      </c>
+      <c r="AG4">
+        <v>2.32</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["59", "67", "78", "89"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.22</v>
       </c>
-      <c r="Z4">
-        <v>3.7</v>
-      </c>
-      <c r="AA4">
-        <v>1.73</v>
-      </c>
-      <c r="AB4">
-        <v>2</v>
-      </c>
-      <c r="AC4">
-        <v>2.9</v>
-      </c>
-      <c r="AD4">
-        <v>1.37</v>
-      </c>
-      <c r="AE4">
-        <v>1.14</v>
-      </c>
-      <c r="AF4">
-        <v>1.57</v>
-      </c>
-      <c r="AG4">
-        <v>2.3</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.29</v>
-      </c>
       <c r="AK4">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.85</v>
+        <v>6.35</v>
       </c>
       <c r="O5">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="P5">
         <v>1.39</v>
@@ -1136,65 +1136,65 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="V5">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
+        <v>1.12</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.2</v>
+      </c>
+      <c r="Z5">
+        <v>4.1</v>
+      </c>
+      <c r="AA5">
+        <v>1.64</v>
+      </c>
+      <c r="AB5">
+        <v>2.13</v>
+      </c>
+      <c r="AC5">
+        <v>2.62</v>
+      </c>
+      <c r="AD5">
+        <v>1.49</v>
+      </c>
+      <c r="AE5">
         <v>1.13</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.14</v>
-      </c>
-      <c r="Z5">
-        <v>5</v>
-      </c>
-      <c r="AA5">
-        <v>1.51</v>
-      </c>
-      <c r="AB5">
-        <v>2.27</v>
-      </c>
-      <c r="AC5">
-        <v>2.27</v>
-      </c>
-      <c r="AD5">
-        <v>1.57</v>
-      </c>
-      <c r="AE5">
+      <c r="AF5">
+        <v>1.81</v>
+      </c>
+      <c r="AG5">
+        <v>1.85</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.22</v>
-      </c>
-      <c r="AF5">
-        <v>1.79</v>
-      </c>
-      <c r="AG5">
-        <v>1.92</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.2</v>
       </c>
       <c r="AK5">
         <v>1.1</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="R6">
         <v>2.21</v>
@@ -1308,7 +1308,7 @@
         <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
         <v>1.51</v>
@@ -1323,19 +1323,19 @@
         <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA6">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
         <v>2.55</v>
       </c>
       <c r="AD6">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE6">
         <v>1.2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.31</v>
+        <v>5.38</v>
       </c>
       <c r="O7">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>2.65</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
-        <v>3.65</v>
+        <v>6.35</v>
       </c>
       <c r="R7">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="S7">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="U7">
-        <v>4.1</v>
+        <v>2.77</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>2.29</v>
+        <v>3.25</v>
       </c>
       <c r="AA7">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="AB7">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O8">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P8">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R8">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="S8">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
         <v>2.25</v>
       </c>
       <c r="U8">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="V8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y8">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Z8">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AA8">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AB8">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AC8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AD8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG8">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="P9">
-        <v>1.5</v>
+        <v>3.11</v>
       </c>
       <c r="Q9">
-        <v>6.18</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="T9">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="U9">
-        <v>2.73</v>
+        <v>4.4</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
+        <v>1.11</v>
+      </c>
+      <c r="Y9">
+        <v>1.66</v>
+      </c>
+      <c r="Z9">
+        <v>2.16</v>
+      </c>
+      <c r="AA9">
+        <v>2.85</v>
+      </c>
+      <c r="AB9">
+        <v>1.32</v>
+      </c>
+      <c r="AC9">
+        <v>7</v>
+      </c>
+      <c r="AD9">
+        <v>1.06</v>
+      </c>
+      <c r="AE9">
         <v>1.03</v>
       </c>
-      <c r="Y9">
-        <v>1.29</v>
-      </c>
-      <c r="Z9">
-        <v>3.3</v>
-      </c>
-      <c r="AA9">
-        <v>1.94</v>
-      </c>
-      <c r="AB9">
-        <v>1.76</v>
-      </c>
-      <c r="AC9">
-        <v>3.6</v>
-      </c>
-      <c r="AD9">
-        <v>1.25</v>
-      </c>
-      <c r="AE9">
-        <v>1.06</v>
-      </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O10">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P10">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
       <c r="Q10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R10">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S10">
         <v>1.62</v>
       </c>
       <c r="T10">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="V10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
         <v>1.01</v>
       </c>
       <c r="X10">
+        <v>1.15</v>
+      </c>
+      <c r="Y10">
+        <v>1.7</v>
+      </c>
+      <c r="Z10">
+        <v>2.1</v>
+      </c>
+      <c r="AA10">
+        <v>3.1</v>
+      </c>
+      <c r="AB10">
+        <v>1.29</v>
+      </c>
+      <c r="AC10">
+        <v>6.5</v>
+      </c>
+      <c r="AD10">
         <v>1.1</v>
       </c>
-      <c r="Y10">
-        <v>1.6</v>
-      </c>
-      <c r="Z10">
-        <v>2.19</v>
-      </c>
-      <c r="AA10">
-        <v>2.9</v>
-      </c>
-      <c r="AB10">
-        <v>1.33</v>
-      </c>
-      <c r="AC10">
-        <v>6</v>
-      </c>
-      <c r="AD10">
-        <v>1.06</v>
-      </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG10">
+        <v>1.5</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.3</v>
+      </c>
+      <c r="AK10">
         <v>1.53</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.33</v>
-      </c>
-      <c r="AK10">
-        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R11">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
+        <v>2.95</v>
+      </c>
+      <c r="U11">
         <v>2.59</v>
       </c>
-      <c r="U11">
-        <v>2.73</v>
-      </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
+        <v>1.24</v>
+      </c>
+      <c r="Z11">
+        <v>3.65</v>
+      </c>
+      <c r="AA11">
+        <v>1.75</v>
+      </c>
+      <c r="AB11">
+        <v>1.95</v>
+      </c>
+      <c r="AC11">
+        <v>3</v>
+      </c>
+      <c r="AD11">
         <v>1.33</v>
       </c>
-      <c r="Z11">
-        <v>3.1</v>
-      </c>
-      <c r="AA11">
-        <v>2</v>
-      </c>
-      <c r="AB11">
-        <v>1.74</v>
-      </c>
-      <c r="AC11">
-        <v>3.55</v>
-      </c>
-      <c r="AD11">
-        <v>1.24</v>
-      </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="P12">
         <v>9.5</v>
       </c>
       <c r="Q12">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="R12">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="U12">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="V12">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
+        <v>1.12</v>
+      </c>
+      <c r="Z12">
+        <v>5.1</v>
+      </c>
+      <c r="AA12">
+        <v>1.36</v>
+      </c>
+      <c r="AB12">
+        <v>2.88</v>
+      </c>
+      <c r="AC12">
+        <v>2</v>
+      </c>
+      <c r="AD12">
+        <v>1.75</v>
+      </c>
+      <c r="AE12">
+        <v>1.32</v>
+      </c>
+      <c r="AF12">
+        <v>1.85</v>
+      </c>
+      <c r="AG12">
+        <v>1.83</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.1</v>
       </c>
-      <c r="Z12">
-        <v>6</v>
-      </c>
-      <c r="AA12">
-        <v>1.42</v>
-      </c>
-      <c r="AB12">
-        <v>2.62</v>
-      </c>
-      <c r="AC12">
-        <v>2.1</v>
-      </c>
-      <c r="AD12">
-        <v>1.68</v>
-      </c>
-      <c r="AE12">
-        <v>1.29</v>
-      </c>
-      <c r="AF12">
-        <v>1.8</v>
-      </c>
-      <c r="AG12">
-        <v>1.88</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.08</v>
-      </c>
       <c r="AK12">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,61 +2431,61 @@
         <v>1.44</v>
       </c>
       <c r="O13">
-        <v>4.58</v>
+        <v>4.25</v>
       </c>
       <c r="P13">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="Q13">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R13">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="U13">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.24</v>
+        <v>4.86</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AC13">
-        <v>2.64</v>
+        <v>2.34</v>
       </c>
       <c r="AD13">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF13">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="Q14">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
         <v>1.04</v>
       </c>
-      <c r="X14">
-        <v>1.05</v>
-      </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA14">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB14">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC14">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P15">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q15">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="R15">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U15">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA15">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AC15">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AD15">
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="P16">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R16">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="V16">
+        <v>1.7</v>
+      </c>
+      <c r="W16">
+        <v>1.16</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.11</v>
+      </c>
+      <c r="Z16">
+        <v>5.15</v>
+      </c>
+      <c r="AA16">
+        <v>1.44</v>
+      </c>
+      <c r="AB16">
+        <v>2.53</v>
+      </c>
+      <c r="AC16">
+        <v>2.32</v>
+      </c>
+      <c r="AD16">
         <v>1.62</v>
       </c>
-      <c r="W16">
-        <v>1.13</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.17</v>
-      </c>
-      <c r="Z16">
-        <v>5</v>
-      </c>
-      <c r="AA16">
-        <v>1.6</v>
-      </c>
-      <c r="AB16">
-        <v>2.3</v>
-      </c>
-      <c r="AC16">
-        <v>2.39</v>
-      </c>
-      <c r="AD16">
-        <v>1.5</v>
-      </c>
       <c r="AE16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK16">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R17">
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T17">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="U17">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z17">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC17">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="AD17">
         <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG17">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
+        <v>1.4</v>
+      </c>
+      <c r="AK17">
         <v>1.44</v>
-      </c>
-      <c r="AK17">
-        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="R18">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S18">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
         <v>2.8</v>
@@ -3273,34 +3273,34 @@
         <v>1.06</v>
       </c>
       <c r="X18">
+        <v>1.04</v>
+      </c>
+      <c r="Y18">
+        <v>1.28</v>
+      </c>
+      <c r="Z18">
+        <v>3.18</v>
+      </c>
+      <c r="AA18">
+        <v>1.99</v>
+      </c>
+      <c r="AB18">
+        <v>1.75</v>
+      </c>
+      <c r="AC18">
+        <v>3.5</v>
+      </c>
+      <c r="AD18">
+        <v>1.28</v>
+      </c>
+      <c r="AE18">
         <v>1.05</v>
       </c>
-      <c r="Y18">
-        <v>1.27</v>
-      </c>
-      <c r="Z18">
-        <v>3.25</v>
-      </c>
-      <c r="AA18">
-        <v>1.98</v>
-      </c>
-      <c r="AB18">
-        <v>1.78</v>
-      </c>
-      <c r="AC18">
-        <v>3.42</v>
-      </c>
-      <c r="AD18">
-        <v>1.29</v>
-      </c>
-      <c r="AE18">
-        <v>1.08</v>
-      </c>
       <c r="AF18">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
         <v>1.67</v>

--- a/jogos_2026-08-11.xlsx
+++ b/jogos_2026-08-11.xlsx
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -787,14 +787,14 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["117", "51", "76"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "88"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "30"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "30"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "77"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "88", "90+4"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,139 +1581,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O8">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P8">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="Q8">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U8">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1.11</v>
+      </c>
+      <c r="Y8">
+        <v>1.66</v>
+      </c>
+      <c r="Z8">
+        <v>2.16</v>
+      </c>
+      <c r="AA8">
+        <v>2.85</v>
+      </c>
+      <c r="AB8">
+        <v>1.32</v>
+      </c>
+      <c r="AC8">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>1.06</v>
+      </c>
+      <c r="AE8">
         <v>1.03</v>
       </c>
-      <c r="X8">
-        <v>1.13</v>
-      </c>
-      <c r="Y8">
-        <v>1.59</v>
-      </c>
-      <c r="Z8">
-        <v>2.21</v>
-      </c>
-      <c r="AA8">
-        <v>2.78</v>
-      </c>
-      <c r="AB8">
-        <v>1.37</v>
-      </c>
-      <c r="AC8">
-        <v>6</v>
-      </c>
-      <c r="AD8">
-        <v>1.08</v>
-      </c>
-      <c r="AE8">
-        <v>1.01</v>
-      </c>
       <c r="AF8">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AG8">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "67", "75"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "60", "80"]</t>
         </is>
       </c>
       <c r="AJ8">
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,22 +1744,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1768,115 +1768,115 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
+        <v>2.6</v>
+      </c>
+      <c r="O9">
+        <v>2.75</v>
+      </c>
+      <c r="P9">
+        <v>2.7</v>
+      </c>
+      <c r="Q9">
+        <v>3.65</v>
+      </c>
+      <c r="R9">
+        <v>1.7</v>
+      </c>
+      <c r="S9">
+        <v>1.57</v>
+      </c>
+      <c r="T9">
         <v>2.25</v>
       </c>
-      <c r="O9">
-        <v>2.7</v>
-      </c>
-      <c r="P9">
-        <v>3.11</v>
-      </c>
-      <c r="Q9">
-        <v>3.25</v>
-      </c>
-      <c r="R9">
-        <v>1.8</v>
-      </c>
-      <c r="S9">
-        <v>1.67</v>
-      </c>
-      <c r="T9">
-        <v>2.2</v>
-      </c>
       <c r="U9">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="V9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1.13</v>
+      </c>
+      <c r="Y9">
+        <v>1.59</v>
+      </c>
+      <c r="Z9">
+        <v>2.21</v>
+      </c>
+      <c r="AA9">
+        <v>2.78</v>
+      </c>
+      <c r="AB9">
+        <v>1.37</v>
+      </c>
+      <c r="AC9">
+        <v>6</v>
+      </c>
+      <c r="AD9">
+        <v>1.08</v>
+      </c>
+      <c r="AE9">
         <v>1.01</v>
       </c>
-      <c r="X9">
-        <v>1.11</v>
-      </c>
-      <c r="Y9">
-        <v>1.66</v>
-      </c>
-      <c r="Z9">
-        <v>2.16</v>
-      </c>
-      <c r="AA9">
-        <v>2.85</v>
-      </c>
-      <c r="AB9">
-        <v>1.32</v>
-      </c>
-      <c r="AC9">
-        <v>7</v>
-      </c>
-      <c r="AD9">
-        <v>1.06</v>
-      </c>
-      <c r="AE9">
-        <v>1.03</v>
-      </c>
       <c r="AF9">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AG9">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ9">
         <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2091,14 +2091,14 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "95"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,11 +2257,11 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "79"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2417,14 +2417,14 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83", "85"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "78"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2746,11 +2746,11 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "66", "72"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
